--- a/artfynd/A 24345-2026 artfynd.xlsx
+++ b/artfynd/A 24345-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136445281</v>
       </c>
       <c r="B2" t="n">
-        <v>96927</v>
+        <v>96930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136447870</v>
       </c>
       <c r="B3" t="n">
-        <v>91508</v>
+        <v>91510</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136444949</v>
       </c>
       <c r="B6" t="n">
-        <v>99619</v>
+        <v>99622</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24345-2026 artfynd.xlsx
+++ b/artfynd/A 24345-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136445281</v>
       </c>
       <c r="B2" t="n">
-        <v>96930</v>
+        <v>96931</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136444949</v>
       </c>
       <c r="B6" t="n">
-        <v>99622</v>
+        <v>99623</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24345-2026 artfynd.xlsx
+++ b/artfynd/A 24345-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136445281</v>
       </c>
       <c r="B2" t="n">
-        <v>96931</v>
+        <v>96936</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136447870</v>
       </c>
       <c r="B3" t="n">
-        <v>91510</v>
+        <v>91512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136444949</v>
       </c>
       <c r="B6" t="n">
-        <v>99623</v>
+        <v>99628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24345-2026 artfynd.xlsx
+++ b/artfynd/A 24345-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136445281</v>
       </c>
       <c r="B2" t="n">
-        <v>96936</v>
+        <v>96938</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136447870</v>
       </c>
       <c r="B3" t="n">
-        <v>91512</v>
+        <v>91514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136444949</v>
       </c>
       <c r="B6" t="n">
-        <v>99628</v>
+        <v>99630</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24345-2026 artfynd.xlsx
+++ b/artfynd/A 24345-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136445281</v>
       </c>
       <c r="B2" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136447870</v>
       </c>
       <c r="B3" t="n">
-        <v>91514</v>
+        <v>91516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136444949</v>
       </c>
       <c r="B6" t="n">
-        <v>99630</v>
+        <v>99636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24345-2026 artfynd.xlsx
+++ b/artfynd/A 24345-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136445281</v>
       </c>
       <c r="B2" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136447870</v>
       </c>
       <c r="B3" t="n">
-        <v>91516</v>
+        <v>91518</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136444949</v>
       </c>
       <c r="B6" t="n">
-        <v>99636</v>
+        <v>99638</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24345-2026 artfynd.xlsx
+++ b/artfynd/A 24345-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136445281</v>
       </c>
       <c r="B2" t="n">
-        <v>96946</v>
+        <v>96947</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136447870</v>
       </c>
       <c r="B3" t="n">
-        <v>91518</v>
+        <v>91519</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>136444949</v>
       </c>
       <c r="B6" t="n">
-        <v>99638</v>
+        <v>99639</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
